--- a/Assets/Resource/King/Event.xlsx
+++ b/Assets/Resource/King/Event.xlsx
@@ -12,69 +12,63 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>招贤纳士</t>
   </si>
   <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>除国王以外，每位玩家都可以花一块钱买一个随机角色，最多能买一次。</t>
+  </si>
+  <si>
+    <t>风调雨顺</t>
+  </si>
+  <si>
     <t>2</t>
   </si>
   <si>
-    <t>除国王以外，每位玩家都可以花一块钱买一个随机角色，最多能买一次。</t>
-  </si>
-  <si>
-    <t>人才市场</t>
+    <t>国王获得1d6块钱。</t>
+  </si>
+  <si>
+    <t>五谷丰登</t>
+  </si>
+  <si>
+    <t>国王获得2d6块钱。</t>
+  </si>
+  <si>
+    <t>明察秋毫</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>除国王以外，每位玩家都可以花一块钱买一个随机角色，最多能买两次。</t>
-  </si>
-  <si>
-    <t>风调雨顺</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>国王获得1d6块钱。</t>
-  </si>
-  <si>
-    <t>五谷丰登</t>
-  </si>
-  <si>
-    <t>国王获得2d6块钱。</t>
+    <t>国王在上朝阶段可以预先查看一名玩家派来的上朝角色，再决定是否接见和搜查。</t>
   </si>
   <si>
     <t>群英荟萃</t>
   </si>
   <si>
-    <t>除国王以外，每名玩家随机获得了一个新的角色。</t>
+    <t>包括国王，每名玩家随机获得了一个新的角色。</t>
   </si>
   <si>
     <t>狼烟四起</t>
   </si>
   <si>
-    <t>本回合发动政变，反贼一方成功所需要的最低力量减一。</t>
+    <t>本回合发动政变，反贼一方成功所需要的最低力量减0.5。</t>
   </si>
   <si>
     <t>削藩罢郡</t>
   </si>
   <si>
-    <t>本回合发动政变，反贼一方成功所需要的最低力量加一。</t>
+    <t>本回合发动政变，反贼一方成功所需要的最低力量加0.5。</t>
   </si>
   <si>
     <t>地方叛乱</t>
   </si>
   <si>
     <t>本回合结束时，如果本回合内国王没有发生更换，则当前的国王必须让位，由其右手边的下一名玩家担任新国王。</t>
-  </si>
-  <si>
-    <t>大赦天下</t>
-  </si>
-  <si>
-    <t>本回合的接见阶段，除了刺杀和政变以外，被搜查导致扣钱时都不会扣钱。</t>
   </si>
   <si>
     <t>多事之秋</t>
@@ -126,7 +120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -156,18 +150,18 @@
         <v>6</v>
       </c>
       <c r="B3" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="0" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" s="0" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>10</v>
@@ -178,7 +172,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C5" s="0" t="s">
         <v>12</v>
@@ -189,7 +183,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C6" s="0" t="s">
         <v>14</v>
@@ -200,7 +194,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C7" s="0" t="s">
         <v>16</v>
@@ -211,7 +205,7 @@
         <v>17</v>
       </c>
       <c r="B8" s="0" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C8" s="0" t="s">
         <v>18</v>
@@ -222,21 +216,10 @@
         <v>19</v>
       </c>
       <c r="B9" s="0" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C9" s="0" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C10" s="0" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resource/King/Event.xlsx
+++ b/Assets/Resource/King/Event.xlsx
@@ -12,57 +12,78 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
-  <si>
-    <t>招贤纳士</t>
-  </si>
-  <si>
-    <t>4</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>人才市场</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>除国王以外，每位玩家都可以花一块钱买一个随机角色，最多能买一次。</t>
   </si>
   <si>
-    <t>风调雨顺</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>国王获得1d6块钱。</t>
-  </si>
-  <si>
-    <t>五谷丰登</t>
+    <t>人才集市</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>除国王以外，每位玩家都可以花一块钱买一个随机角色，买第2次时则需要花两块，以此类推。</t>
+  </si>
+  <si>
+    <t>丰收</t>
   </si>
   <si>
     <t>国王获得2d6块钱。</t>
   </si>
   <si>
-    <t>明察秋毫</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>国王在上朝阶段可以预先查看一名玩家派来的上朝角色，再决定是否接见和搜查。</t>
-  </si>
-  <si>
-    <t>群英荟萃</t>
-  </si>
-  <si>
-    <t>包括国王，每名玩家随机获得了一个新的角色。</t>
-  </si>
-  <si>
-    <t>狼烟四起</t>
-  </si>
-  <si>
-    <t>本回合发动政变，反贼一方成功所需要的最低力量减0.5。</t>
-  </si>
-  <si>
-    <t>削藩罢郡</t>
-  </si>
-  <si>
-    <t>本回合发动政变，反贼一方成功所需要的最低力量加0.5。</t>
+    <t>人口红利</t>
+  </si>
+  <si>
+    <t>包括国王，每名玩家随机获得一个新的角色。</t>
+  </si>
+  <si>
+    <t>军心动乱</t>
+  </si>
+  <si>
+    <t>本回合发动政变，反贼一方成功所需要的最低力量减1。</t>
+  </si>
+  <si>
+    <t>戒严</t>
+  </si>
+  <si>
+    <t>本回合发动政变，反贼一方成功所需要的最低力量加1。</t>
+  </si>
+  <si>
+    <t>祭祀</t>
+  </si>
+  <si>
+    <t>每名玩家握住一定数量钱，然后同时展示并且上交国库，若总共的钱大于等于（2*玩家数），每名玩家获得1d6块钱并且国王获得的钱翻倍。</t>
+  </si>
+  <si>
+    <t>多元化</t>
+  </si>
+  <si>
+    <t>准备上朝时可以将两个不同角色一起上朝，国王只能都搜或者都不搜，只要有一个搜查正确则视为搜查正确。</t>
+  </si>
+  <si>
+    <t>严政</t>
+  </si>
+  <si>
+    <t>搜查时，若正确国王获得两块钱，若错误则国王家族扣一块钱交给对方。</t>
+  </si>
+  <si>
+    <t>征税</t>
+  </si>
+  <si>
+    <t>每名玩家统计并公开自己的家族财产，财产最多的玩家都需要上交两块钱到国库（如果财产小于10则不用）。</t>
+  </si>
+  <si>
+    <t>大一统</t>
+  </si>
+  <si>
+    <t>如果这一回合没有政变，则国王只能选择对所有的人都进行搜查或者都不搜查，接见顺序仍由国王决定。</t>
   </si>
   <si>
     <t>地方叛乱</t>
@@ -74,7 +95,10 @@
     <t>多事之秋</t>
   </si>
   <si>
-    <t>本事件卡无效，再抽取两张事件卡。</t>
+    <t>5</t>
+  </si>
+  <si>
+    <t>本事件卡无效，再抽取两张事件卡（如果再抽出的事件卡为多事之秋，则将其塞到之后的位置并且重新抽取）。</t>
   </si>
 </sst>
 </file>
@@ -120,7 +144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -150,7 +174,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>7</v>
@@ -161,65 +185,109 @@
         <v>8</v>
       </c>
       <c r="B4" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="0" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" s="0" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="0" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="0" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="0" t="s">
         <v>13</v>
-      </c>
-      <c r="B6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="0" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="0" t="s">
         <v>15</v>
-      </c>
-      <c r="B7" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="0" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="0" t="s">
         <v>17</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="0" t="s">
+    </row>
+    <row r="10">
+      <c r="A10" s="0" t="s">
         <v>20</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="C12" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="C13" s="0" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
